--- a/pipeline_engineer/ui/assembly_manager/specifications/specifications.xlsx
+++ b/pipeline_engineer/ui/assembly_manager/specifications/specifications.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Pipeline Assembly List" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="47">
   <si>
     <t xml:space="preserve">assembly</t>
   </si>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t xml:space="preserve">sdr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header_sdr</t>
   </si>
 </sst>
 </file>
@@ -433,7 +439,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -653,7 +659,7 @@
       <c r="J12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P12" s="0" t="s">
+      <c r="P12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3800,7 +3806,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3816,6 +3822,16 @@
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
